--- a/Design/Excel/ET/Datas/Product/GridBakeRecipeConfig.xlsx
+++ b/Design/Excel/ET/Datas/Product/GridBakeRecipeConfig.xlsx
@@ -939,266 +939,276 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <x:cols>
-    <x:col min="1" max="1" width="21.125" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="12.75" style="2" customWidth="1"/>
-    <x:col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="15.125" style="2" customWidth="1"/>
-    <x:col min="6" max="6" width="9.625" style="2" customWidth="1"/>
-    <x:col min="7" max="7" width="28.75" style="2" customWidth="1"/>
-    <x:col min="8" max="9" width="11.75" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="6.75" style="2" customWidth="1"/>
-    <x:col min="11" max="16384" width="9" style="2" customWidth="0"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##var</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InputDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OutputDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StationCapability</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RequiredTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G1" t="str">
-        <x:v>CarrierDefinitionId</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##type</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G2" t="str">
-        <x:v>int</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">##</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Id</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">InputDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">OutputDefinitionId</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">StationCapability</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">RequiredTicks</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" t="str">
-        <x:v>烘焙载具定义（0为直接物件）</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve"/>
-        </x:is>
-      </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">8</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">9</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">80</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="str"/>
-      <x:c r="B5" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" t="n">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="D5" t="n">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="E5" t="n">
-        <x:v>4096</x:v>
-      </x:c>
-      <x:c r="F5" t="n">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="str"/>
-      <x:c r="B6" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C6" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D6" t="n">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E6" t="n">
-        <x:v>4096</x:v>
-      </x:c>
-      <x:c r="F6" t="n">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="str"/>
-      <x:c r="B7" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D7" t="n">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E7" t="n">
-        <x:v>4096</x:v>
-      </x:c>
-      <x:c r="F7" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G7" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="str"/>
-      <x:c r="B8" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" t="n">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D8" t="n">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="E8" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F8" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G8" t="n">
-        <x:v>47</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="str"/>
-      <x:c r="B9" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C9" t="n">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D9" t="n">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E9" t="n">
-        <x:v>16384</x:v>
-      </x:c>
-      <x:c r="F9" t="n">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
+    <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="9.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="28.75" style="2" customWidth="1"/>
+    <col min="8" max="9" width="11.75" style="2" customWidth="1"/>
+    <col min="10" max="10" width="6.75" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="2" customWidth="0"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InputDefinitionId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OutputDefinitionId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StationCapability</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RequiredTicks</t>
+        </is>
+      </c>
+      <c r="G1" t="str">
+        <v>CarrierDefinitionId</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##type</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>GridStationCapability</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">int</t>
+        </is>
+      </c>
+      <c r="G2" t="str">
+        <v>int</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">##</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Id</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InputDefinitionId</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OutputDefinitionId</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">StationCapability</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RequiredTicks</t>
+        </is>
+      </c>
+      <c r="G3" t="str">
+        <v>烘焙载具定义（0为直接物件）</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str"/>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>33</v>
+      </c>
+      <c r="D5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>80</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str"/>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="n">
+        <v>35</v>
+      </c>
+      <c r="D6" t="n">
+        <v>36</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>70</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str"/>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>37</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Fry</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>60</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str"/>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>46</v>
+      </c>
+      <c r="D8" t="n">
+        <v>48</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Bake</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>100</v>
+      </c>
+      <c r="G8" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str"/>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="n">
+        <v>52</v>
+      </c>
+      <c r="D9" t="n">
+        <v>53</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Grind</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>40</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>